--- a/tests/data/bulk-upload-template.xlsx
+++ b/tests/data/bulk-upload-template.xlsx
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Ahmed40560</v>
+        <v>Ahmed52090</v>
       </c>
       <c r="B3" t="str">
         <v>Hassan</v>
       </c>
       <c r="C3" t="str">
-        <v>+919815157013</v>
+        <v>+919813994413</v>
       </c>
       <c r="D3" t="str">
         <v>India</v>
@@ -462,7 +462,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F3" t="str">
-        <v>784-1987-7725059-6</v>
+        <v>784-1989-3341365-4</v>
       </c>
       <c r="G3" t="str">
         <v>no</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sara40561</v>
+        <v>Sara52091</v>
       </c>
       <c r="B4" t="str">
         <v>Mansour</v>
       </c>
       <c r="C4" t="str">
-        <v>+919820792738</v>
+        <v>+919818558957</v>
       </c>
       <c r="D4" t="str">
         <v>India</v>
@@ -485,7 +485,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F4" t="str">
-        <v>784-1978-7498430-2</v>
+        <v>784-1982-9162752-4</v>
       </c>
       <c r="G4" t="str">
         <v>no</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Omar40562</v>
+        <v>Omar52092</v>
       </c>
       <c r="B5" t="str">
         <v>Saleh</v>
       </c>
       <c r="C5" t="str">
-        <v>+919834155205</v>
+        <v>+919837948851</v>
       </c>
       <c r="D5" t="str">
         <v>India</v>
@@ -508,7 +508,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F5" t="str">
-        <v>784-1965-9855012-4</v>
+        <v>784-1991-5371127-3</v>
       </c>
       <c r="G5" t="str">
         <v>no</v>
@@ -516,13 +516,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Layla40563</v>
+        <v>Layla52093</v>
       </c>
       <c r="B6" t="str">
         <v>Nasser</v>
       </c>
       <c r="C6" t="str">
-        <v>+919842404890</v>
+        <v>+919818985778</v>
       </c>
       <c r="D6" t="str">
         <v>India</v>
@@ -531,7 +531,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F6" t="str">
-        <v>784-1970-2505615-7</v>
+        <v>784-1995-0477146-3</v>
       </c>
       <c r="G6" t="str">
         <v>no</v>
@@ -539,13 +539,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Khalid40564</v>
+        <v>Khalid52094</v>
       </c>
       <c r="B7" t="str">
         <v>Farouk</v>
       </c>
       <c r="C7" t="str">
-        <v>+919895993123</v>
+        <v>+919828336216</v>
       </c>
       <c r="D7" t="str">
         <v>India</v>
@@ -554,7 +554,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F7" t="str">
-        <v>784-1983-9747404-6</v>
+        <v>784-1967-0232617-2</v>
       </c>
       <c r="G7" t="str">
         <v>no</v>
